--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post FET_HRM-2031-0472/panel_11/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post FET_HRM-2031-0472/panel_11/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.36282</v>
+        <v>17.32945</v>
       </c>
       <c r="D2" t="n">
-        <v>17.01889</v>
+        <v>17.09564</v>
       </c>
       <c r="E2" t="n">
-        <v>17.34243</v>
+        <v>17.3168</v>
       </c>
       <c r="F2" t="n">
-        <v>44.25238</v>
+        <v>43.91182</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05304</v>
+        <v>0.05288</v>
       </c>
       <c r="H2" t="n">
-        <v>1.86931</v>
+        <v>1.90779</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.06547</v>
+        <v>17.452</v>
       </c>
       <c r="D3" t="n">
-        <v>17.2387</v>
+        <v>16.69018</v>
       </c>
       <c r="E3" t="n">
-        <v>17.28029</v>
+        <v>17.43284</v>
       </c>
       <c r="F3" t="n">
-        <v>44.0902</v>
+        <v>44.77949</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05312</v>
+        <v>0.05203</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8566</v>
+        <v>1.89615</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.43385</v>
+        <v>17.83748</v>
       </c>
       <c r="D4" t="n">
-        <v>17.55035</v>
+        <v>16.87888</v>
       </c>
       <c r="E4" t="n">
-        <v>17.27608</v>
+        <v>17.35852</v>
       </c>
       <c r="F4" t="n">
-        <v>43.85646</v>
+        <v>44.17822</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05125</v>
+        <v>0.05287</v>
       </c>
       <c r="H4" t="n">
-        <v>1.86922</v>
+        <v>1.86013</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.23768</v>
+        <v>17.36999</v>
       </c>
       <c r="D6" t="n">
-        <v>16.54467</v>
+        <v>16.49126</v>
       </c>
       <c r="E6" t="n">
-        <v>17.02887</v>
+        <v>17.01329</v>
       </c>
       <c r="F6" t="n">
-        <v>22.40716</v>
+        <v>21.91318</v>
       </c>
       <c r="G6" t="n">
-        <v>34.62582</v>
+        <v>34.74105</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.57599</v>
+        <v>17.20099</v>
       </c>
       <c r="D7" t="n">
-        <v>16.54722</v>
+        <v>16.28278</v>
       </c>
       <c r="E7" t="n">
-        <v>17.07966</v>
+        <v>16.85598</v>
       </c>
       <c r="F7" t="n">
-        <v>22.28948</v>
+        <v>22.74633</v>
       </c>
       <c r="G7" t="n">
-        <v>35.23593</v>
+        <v>35.5876</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.344</v>
+        <v>16.99417</v>
       </c>
       <c r="D8" t="n">
-        <v>16.48906</v>
+        <v>16.62279</v>
       </c>
       <c r="E8" t="n">
-        <v>16.6333</v>
+        <v>16.9335</v>
       </c>
       <c r="F8" t="n">
-        <v>22.46831</v>
+        <v>22.53353</v>
       </c>
       <c r="G8" t="n">
-        <v>34.94075</v>
+        <v>35.10459</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6357699999999999</v>
+        <v>0.61641</v>
       </c>
       <c r="D10" t="n">
-        <v>1.15035</v>
+        <v>1.14596</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6188399999999999</v>
+        <v>0.62266</v>
       </c>
       <c r="D11" t="n">
-        <v>1.16747</v>
+        <v>1.14435</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.63391</v>
+        <v>0.62254</v>
       </c>
       <c r="D12" t="n">
-        <v>1.16283</v>
+        <v>1.11498</v>
       </c>
     </row>
   </sheetData>
